--- a/exports/NESTLEIND_full_report.xlsx
+++ b/exports/NESTLEIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>2.01</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44578.38541666666</v>
+        <v>44578.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>968</v>
+        <v>964.7</v>
       </c>
       <c r="I2" t="n">
         <v>965.9799999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.81</v>
+        <v>-2.14</v>
       </c>
       <c r="L2" t="n">
-        <v>2.26</v>
+        <v>3.06</v>
       </c>
       <c r="M2" t="n">
         <v>0.76</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>2.8</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44637.38541666666</v>
+        <v>44637.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>898.7</v>
+        <v>915</v>
       </c>
       <c r="I3" t="n">
         <v>902.5977529758426</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>58.83333333333334</v>
+        <v>59</v>
       </c>
       <c r="K3" t="n">
-        <v>6.84</v>
+        <v>5.15</v>
       </c>
       <c r="L3" t="n">
         <v>0.8100000000000001</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>5.64</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44644.55208333334</v>
+        <v>44645.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>867.2</v>
+        <v>856.9</v>
       </c>
       <c r="I4" t="n">
         <v>863.4209687863035</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.22</v>
+        <v>-6.35</v>
       </c>
       <c r="L4" t="n">
-        <v>5.72</v>
+        <v>6.46</v>
       </c>
       <c r="M4" t="n">
         <v>0.6899999999999999</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>5.86</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>877.6</v>
+        <v>886.8</v>
       </c>
       <c r="I5" t="n">
         <v>883.1147262691684</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.42</v>
+        <v>-3.49</v>
       </c>
       <c r="L5" t="n">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="M5" t="n">
         <v>0.8100000000000001</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>4.87</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.55208333334</v>
+        <v>44686.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>906.2</v>
+        <v>885</v>
       </c>
       <c r="I6" t="n">
         <v>895.4249435546245</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K6" t="n">
-        <v>2.19</v>
+        <v>-0.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.51</v>
@@ -783,7 +854,7 @@
         <v>1.57</v>
       </c>
       <c r="N6" t="n">
-        <v>1.99</v>
+        <v>3.09</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.39</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>806.5</v>
+        <v>844.8</v>
       </c>
       <c r="I7" t="n">
         <v>839.1351470215745</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>8.869999999999999</v>
+        <v>4.54</v>
       </c>
       <c r="L7" t="n">
         <v>3.83</v>
@@ -840,7 +923,7 @@
         <v>1.64</v>
       </c>
       <c r="N7" t="n">
-        <v>0.96</v>
+        <v>3.96</v>
       </c>
       <c r="O7" t="n">
         <v>-3.09</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>6.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="I8" t="n">
         <v>846.7240054743066</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>0.62</v>
+        <v>-1.04</v>
       </c>
       <c r="L8" t="n">
         <v>3.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="N8" t="n">
         <v>2.54</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.99</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44741.38541666666</v>
+        <v>44741.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>871.4</v>
+        <v>876</v>
       </c>
       <c r="I9" t="n">
         <v>871.5625504320469</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.23</v>
+        <v>-4.78</v>
       </c>
       <c r="L9" t="n">
-        <v>4.67</v>
+        <v>4.81</v>
       </c>
       <c r="M9" t="n">
         <v>1.38</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.22</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44809.55208333334</v>
+        <v>44810.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>961.4</v>
+        <v>954.5</v>
       </c>
       <c r="I10" t="n">
         <v>957.9948632156853</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>68</v>
+        <v>68.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>9.75</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>1.63</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>4.15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>948.3</v>
+        <v>964</v>
       </c>
       <c r="I11" t="n">
         <v>958.1087096566999</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K11" t="n">
-        <v>0.65</v>
+        <v>-1</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="N11" t="n">
         <v>1.57</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>4.66</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44845.38541666666</v>
+        <v>44845.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>940</v>
+        <v>926.2</v>
       </c>
       <c r="I12" t="n">
         <v>931.0071280148741</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.49</v>
+        <v>-3.92</v>
       </c>
       <c r="L12" t="n">
-        <v>2.49</v>
+        <v>4.51</v>
       </c>
       <c r="M12" t="n">
         <v>0.68</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>4.54</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44852.38541666666</v>
+        <v>44852.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>964</v>
+        <v>968.8</v>
       </c>
       <c r="I13" t="n">
         <v>966.173503478497</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.08</v>
+        <v>-4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>4.57</v>
+        <v>4.88</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>3.9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>995</v>
+        <v>986</v>
       </c>
       <c r="I14" t="n">
         <v>989.3908777108888</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>31</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="L14" t="n">
         <v>0.71</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>3.74</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44893.55208333334</v>
+        <v>44894.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>986.5</v>
+        <v>1009.8</v>
       </c>
       <c r="I15" t="n">
         <v>1009.611487861669</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.05</v>
+        <v>-2.41</v>
       </c>
       <c r="L15" t="n">
-        <v>0.78</v>
+        <v>3.33</v>
       </c>
       <c r="M15" t="n">
         <v>0.51</v>
       </c>
       <c r="N15" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="O15" t="n">
         <v>-0.44</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.64</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44910.38541666666</v>
+        <v>44910.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>991.5</v>
+        <v>985.7</v>
       </c>
       <c r="I16" t="n">
         <v>988.5110457332922</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.81</v>
+        <v>-2.39</v>
       </c>
       <c r="L16" t="n">
         <v>3.19</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>3.85</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44972.55208333334</v>
+        <v>44973.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>962.5</v>
+        <v>984.1</v>
       </c>
       <c r="I17" t="n">
         <v>972.1529328193409</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>62</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K17" t="n">
-        <v>2.35</v>
+        <v>0.16</v>
       </c>
       <c r="L17" t="n">
         <v>3.76</v>
       </c>
       <c r="M17" t="n">
-        <v>0.62</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="O17" t="n">
         <v>-1.72</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44974.55208333334</v>
+        <v>44977.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>950.1</v>
+        <v>941.8</v>
       </c>
       <c r="I18" t="n">
         <v>949.9298743992468</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.45</v>
+        <v>-4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="M18" t="n">
         <v>0.12</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.85</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45001.55208333334</v>
+        <v>45002.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>920.2</v>
+        <v>940.6</v>
       </c>
       <c r="I19" t="n">
         <v>925.7014268268478</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
-        <v>2.29</v>
+        <v>0.13</v>
       </c>
       <c r="L19" t="n">
         <v>1.42</v>
@@ -1524,7 +1751,7 @@
         <v>0.54</v>
       </c>
       <c r="N19" t="n">
-        <v>2.19</v>
+        <v>2.53</v>
       </c>
       <c r="O19" t="n">
         <v>-0.92</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.45</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45069.55208333334</v>
+        <v>45070.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1071</v>
+        <v>1064.7</v>
       </c>
       <c r="I20" t="n">
         <v>1068.900698343697</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K20" t="n">
-        <v>13.86</v>
+        <v>13.19</v>
       </c>
       <c r="L20" t="n">
         <v>1.79</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>3.4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1091</v>
+        <v>1102.7</v>
       </c>
       <c r="I21" t="n">
         <v>1097.927741639136</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.47</v>
+        <v>-3.57</v>
       </c>
       <c r="L21" t="n">
-        <v>2.96</v>
+        <v>3.64</v>
       </c>
       <c r="M21" t="n">
-        <v>0.57</v>
+        <v>0.82</v>
       </c>
       <c r="N21" t="n">
         <v>0.95</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.62</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45133.55208333334</v>
+        <v>45134.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1139.2</v>
+        <v>1109.4</v>
       </c>
       <c r="I22" t="n">
         <v>1121.502871349766</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.31</v>
+        <v>0.61</v>
       </c>
       <c r="L22" t="n">
         <v>1.98</v>
@@ -1695,7 +1958,7 @@
         <v>0.52</v>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="O22" t="n">
         <v>0.93</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.16</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1107.5</v>
+        <v>1119</v>
       </c>
       <c r="I23" t="n">
         <v>1116.885466668568</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K23" t="n">
-        <v>0.17</v>
+        <v>-0.87</v>
       </c>
       <c r="L23" t="n">
         <v>3.38</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.84</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45274.55208333334</v>
+        <v>45275.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1240</v>
+        <v>1214.4</v>
       </c>
       <c r="I24" t="n">
         <v>1216.945215819647</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>93.16666666666667</v>
+        <v>94</v>
       </c>
       <c r="K24" t="n">
-        <v>10.81</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>1.63</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.96</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45278.55208333334</v>
+        <v>45279.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1215</v>
+        <v>1265.5</v>
       </c>
       <c r="I25" t="n">
         <v>1258.671314841597</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.05</v>
+        <v>-4.21</v>
       </c>
       <c r="L25" t="n">
-        <v>2.73</v>
+        <v>5.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2</v>
+        <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="O25" t="n">
         <v>-1.56</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.37</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45299.55208333334</v>
+        <v>45300.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1315</v>
+        <v>1297</v>
       </c>
       <c r="I26" t="n">
         <v>1313.684688066921</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
-        <v>3.91</v>
+        <v>2.49</v>
       </c>
       <c r="L26" t="n">
         <v>3.15</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45341.55208333334</v>
+        <v>45342.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1257.6</v>
+        <v>1267.2</v>
       </c>
       <c r="I27" t="n">
         <v>1264.148909165629</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K27" t="n">
-        <v>3.04</v>
+        <v>2.3</v>
       </c>
       <c r="L27" t="n">
         <v>1.79</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>4.39</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45369.55208333334</v>
+        <v>45370.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1291.9</v>
+        <v>1245.2</v>
       </c>
       <c r="I28" t="n">
         <v>1255.627797643072</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>1.95</v>
+        <v>-1.74</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>2.61</v>
       </c>
       <c r="M28" t="n">
         <v>0.47</v>
       </c>
       <c r="N28" t="n">
-        <v>1.92</v>
+        <v>3.13</v>
       </c>
       <c r="O28" t="n">
         <v>0.95</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.9</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45379.38541666666</v>
+        <v>45379.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1310.1</v>
+        <v>1318.5</v>
       </c>
       <c r="I29" t="n">
         <v>1314.136783535855</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.21</v>
+        <v>-5.89</v>
       </c>
       <c r="L29" t="n">
         <v>5.96</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>5.45</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45387.55208333334</v>
+        <v>45390.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1269.5</v>
+        <v>1250.6</v>
       </c>
       <c r="I30" t="n">
         <v>1254.176515342</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.72</v>
+        <v>-5.15</v>
       </c>
       <c r="L30" t="n">
-        <v>4.66</v>
+        <v>5.38</v>
       </c>
       <c r="M30" t="n">
         <v>0.55</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.25</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45407.38541666666</v>
+        <v>45407.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1275</v>
+        <v>1282</v>
       </c>
       <c r="I31" t="n">
         <v>1280.98706387935</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.95</v>
+        <v>-2.51</v>
       </c>
       <c r="L31" t="n">
         <v>3.29</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>5.25</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1234.2</v>
+        <v>1208.6</v>
       </c>
       <c r="I32" t="n">
         <v>1214.653237069765</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.73</v>
+        <v>-5.73</v>
       </c>
       <c r="L32" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="M32" t="n">
         <v>1.36</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>4.91</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1216.1</v>
+        <v>1251.8</v>
       </c>
       <c r="I33" t="n">
         <v>1227.107841746401</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.62</v>
+        <v>-3.57</v>
       </c>
       <c r="L33" t="n">
-        <v>2.32</v>
+        <v>6.49</v>
       </c>
       <c r="M33" t="n">
         <v>0.84</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.94</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45497.55208333334</v>
+        <v>45498.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1275.5</v>
+        <v>1233.8</v>
       </c>
       <c r="I34" t="n">
         <v>1268.967967595341</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>1.89</v>
+        <v>-1.44</v>
       </c>
       <c r="L34" t="n">
         <v>2.94</v>
@@ -2379,7 +2786,7 @@
         <v>0.89</v>
       </c>
       <c r="N34" t="n">
-        <v>1.72</v>
+        <v>2.86</v>
       </c>
       <c r="O34" t="n">
         <v>2.79</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.84</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45525.38541666666</v>
+        <v>45525.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1269.6</v>
+        <v>1275</v>
       </c>
       <c r="I35" t="n">
         <v>1273.817842661766</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.9</v>
+        <v>-3.34</v>
       </c>
       <c r="L35" t="n">
         <v>3.61</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>3.27</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1339.2</v>
+        <v>1311.6</v>
       </c>
       <c r="I36" t="n">
         <v>1313.228542785698</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>5.04</v>
+        <v>2.87</v>
       </c>
       <c r="L36" t="n">
         <v>2.43</v>
@@ -2493,7 +2924,7 @@
         <v>0.82</v>
       </c>
       <c r="N36" t="n">
-        <v>1.58</v>
+        <v>2.46</v>
       </c>
       <c r="O36" t="n">
         <v>0.99</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.44</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1097.2</v>
+        <v>1112.2</v>
       </c>
       <c r="I37" t="n">
         <v>1111.022543541142</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>90.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K37" t="n">
-        <v>16.35</v>
+        <v>15.2</v>
       </c>
       <c r="L37" t="n">
         <v>2.1</v>
@@ -2550,7 +2993,7 @@
         <v>1.29</v>
       </c>
       <c r="N37" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="O37" t="n">
         <v>-2.46</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>3.44</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1105</v>
+        <v>1086.5</v>
       </c>
       <c r="I38" t="n">
         <v>1090.96552799611</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.65</v>
+        <v>-2.31</v>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>3.06</v>
       </c>
       <c r="M38" t="n">
         <v>0.27</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.35</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1113</v>
+        <v>1165.7</v>
       </c>
       <c r="I39" t="n">
         <v>1120.746410355723</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.44</v>
+        <v>-7.29</v>
       </c>
       <c r="L39" t="n">
-        <v>3.08</v>
+        <v>9.85</v>
       </c>
       <c r="M39" t="n">
         <v>0.63</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="O39" t="n">
         <v>-1.63</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>7.34</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1112</v>
+        <v>1092.6</v>
       </c>
       <c r="I40" t="n">
         <v>1094.37673665073</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.61</v>
+        <v>-6.27</v>
       </c>
       <c r="L40" t="n">
-        <v>5.37</v>
+        <v>6.31</v>
       </c>
       <c r="M40" t="n">
         <v>0.7</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.26</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45723.55208333334</v>
+        <v>45726.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1112.5</v>
+        <v>1132.4</v>
       </c>
       <c r="I41" t="n">
         <v>1116.950685135953</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.82</v>
+        <v>-3.64</v>
       </c>
       <c r="L41" t="n">
         <v>4.42</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.96</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1192.5</v>
+        <v>1165</v>
       </c>
       <c r="I42" t="n">
         <v>1166.957747486366</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K42" t="n">
-        <v>5.31</v>
+        <v>2.88</v>
       </c>
       <c r="L42" t="n">
         <v>4.84</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.93</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1195.8</v>
+        <v>1200.8</v>
       </c>
       <c r="I43" t="n">
         <v>1198.568979388872</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.64</v>
+        <v>-3.07</v>
       </c>
       <c r="L43" t="n">
         <v>3.64</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>4.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45824.55208333334</v>
+        <v>45825.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1193.5</v>
+        <v>1179.8</v>
       </c>
       <c r="I44" t="n">
         <v>1182.799343943006</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.61</v>
+        <v>-1.75</v>
       </c>
       <c r="L44" t="n">
         <v>2.56</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>3.65</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1187</v>
+        <v>1202.4</v>
       </c>
       <c r="I45" t="n">
         <v>1196.000240879712</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.61</v>
+        <v>-1.92</v>
       </c>
       <c r="L45" t="n">
-        <v>1.66</v>
+        <v>2.93</v>
       </c>
       <c r="M45" t="n">
         <v>1.07</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>3.99</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1225</v>
+        <v>1170.8</v>
       </c>
       <c r="I46" t="n">
         <v>1195.797421396491</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K46" t="n">
-        <v>1.88</v>
+        <v>-2.63</v>
       </c>
       <c r="L46" t="n">
-        <v>1.56</v>
+        <v>3.72</v>
       </c>
       <c r="M46" t="n">
         <v>0.17</v>
       </c>
       <c r="N46" t="n">
-        <v>2.1</v>
+        <v>5.47</v>
       </c>
       <c r="O46" t="n">
         <v>1.31</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>7.19</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1088.5</v>
+        <v>1168.6</v>
       </c>
       <c r="I47" t="n">
         <v>1128.258264281128</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>7.03</v>
+        <v>0.19</v>
       </c>
       <c r="L47" t="n">
         <v>5.7</v>
       </c>
       <c r="M47" t="n">
-        <v>0.49</v>
+        <v>2.94</v>
       </c>
       <c r="N47" t="n">
-        <v>1.26</v>
+        <v>5.32</v>
       </c>
       <c r="O47" t="n">
         <v>-5.47</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.11</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1189.1</v>
+        <v>1171</v>
       </c>
       <c r="I48" t="n">
         <v>1179.84886004208</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K48" t="n">
-        <v>1.75</v>
+        <v>0.21</v>
       </c>
       <c r="L48" t="n">
         <v>4.12</v>
@@ -3177,7 +3752,7 @@
         <v>0.48</v>
       </c>
       <c r="N48" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="O48" t="n">
         <v>5.32</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.3</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45936.55208333334</v>
+        <v>45937.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1181.8</v>
+        <v>1190.7</v>
       </c>
       <c r="I49" t="n">
         <v>1187.892031472029</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.92</v>
+        <v>-1.68</v>
       </c>
       <c r="L49" t="n">
         <v>2.01</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>3.7</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45993.55208333334</v>
+        <v>45994.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1258.1</v>
+        <v>1244</v>
       </c>
       <c r="I50" t="n">
         <v>1245.332053474915</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K50" t="n">
-        <v>5.66</v>
+        <v>4.48</v>
       </c>
       <c r="L50" t="n">
         <v>2.7</v>
@@ -3291,7 +3890,7 @@
         <v>1.22</v>
       </c>
       <c r="N50" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="O50" t="n">
         <v>-0.15</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>3.25</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1243</v>
+        <v>1250.9</v>
       </c>
       <c r="I51" t="n">
         <v>1245.519233160944</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>0.08</v>
+        <v>-0.55</v>
       </c>
       <c r="L51" t="n">
         <v>1.61</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>3.63</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1295.4</v>
+        <v>1268.7</v>
       </c>
       <c r="I52" t="n">
         <v>1271.599532605279</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K52" t="n">
-        <v>3.56</v>
+        <v>1.42</v>
       </c>
       <c r="L52" t="n">
         <v>0.87</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.46</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46121.38541666666</v>
+        <v>46121.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1221.3</v>
+        <v>1230</v>
       </c>
       <c r="I53" t="n">
         <v>1225.84704509294</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>70</v>
+        <v>70.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="L53" t="n">
         <v>5.65</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.29</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1434.9</v>
+        <v>1422</v>
       </c>
       <c r="I54" t="n">
         <v>1426.155121233561</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>36</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K54" t="n">
-        <v>16.66</v>
+        <v>15.61</v>
       </c>
       <c r="L54" t="n">
         <v>1.06</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.8</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46203.55208333334</v>
+        <v>46204.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1413.8</v>
+        <v>1448.3</v>
       </c>
       <c r="I55" t="n">
         <v>1437.484686814088</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K55" t="n">
-        <v>0.58</v>
+        <v>-1.85</v>
       </c>
       <c r="L55" t="n">
         <v>2.31</v>
@@ -3576,7 +4235,7 @@
         <v>2.45</v>
       </c>
       <c r="N55" t="n">
-        <v>2.03</v>
+        <v>2.77</v>
       </c>
       <c r="O55" t="n">
         <v>-0.48</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.94</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1469.2</v>
+        <v>1466</v>
       </c>
       <c r="I56" t="n">
         <v>1468.347381986959</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K56" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="L56" t="n">
         <v>2.98</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.3</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1320.4</v>
+        <v>1364.3</v>
       </c>
       <c r="I57" t="n">
         <v>1343.069816063824</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K57" t="n">
-        <v>9.93</v>
+        <v>6.94</v>
       </c>
       <c r="L57" t="n">
         <v>3.33</v>
@@ -3690,7 +4373,7 @@
         <v>4.15</v>
       </c>
       <c r="N57" t="n">
-        <v>3.08</v>
+        <v>3.73</v>
       </c>
       <c r="O57" t="n">
         <v>-0.63</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>5.72</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46310.38541666666</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>1309.2</v>
+        <v>1282.5</v>
       </c>
       <c r="I58" t="n">
         <v>1298.202470836109</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.04</v>
+        <v>-6</v>
       </c>
       <c r="L58" t="n">
         <v>7.61</v>
       </c>
       <c r="M58" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="N58" t="n">
         <v>6.37</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>17</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5909,7 +6624,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="6">
@@ -5919,7 +6634,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -5929,7 +6644,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>93.2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -5939,7 +6654,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -5949,7 +6664,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -5959,7 +6674,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="11">
@@ -5999,7 +6714,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.57</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="15">
@@ -6009,7 +6724,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.07</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="16">
@@ -6019,7 +6734,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.05</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -6029,7 +6744,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.66</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="18">
@@ -6039,7 +6754,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.4</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="19">
@@ -6049,7 +6764,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.04</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="20">
@@ -6059,7 +6774,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.74</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="21">
@@ -6069,7 +6784,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.61</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="22">
@@ -6079,7 +6794,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -6099,7 +6814,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="25">
@@ -6119,7 +6834,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.14</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="27">
@@ -6139,7 +6854,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
